--- a/df_fPC1/sum.var_AMR_ES_C3G_R.xlsx
+++ b/df_fPC1/sum.var_AMR_ES_C3G_R.xlsx
@@ -722,7 +722,7 @@
         <v>-0.0537738005079313</v>
       </c>
       <c r="I2" t="n">
-        <v>0.100795009558128</v>
+        <v>0.10430318507905</v>
       </c>
       <c r="J2" t="n">
         <v>0.0374203753090823</v>
@@ -883,7 +883,7 @@
         <v>0.0110392913343446</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0358882860738656</v>
+        <v>0.0331468650056</v>
       </c>
       <c r="J3" t="n">
         <v>-0.0977320093276271</v>
@@ -1044,7 +1044,7 @@
         <v>-0.0172861819723365</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.275683944862422</v>
+        <v>-0.288915997476618</v>
       </c>
       <c r="J4" t="n">
         <v>-0.379057941144188</v>
@@ -1205,7 +1205,7 @@
         <v>-0.0948922606611758</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0511182885771347</v>
+        <v>-0.0432775858187159</v>
       </c>
       <c r="J5" t="n">
         <v>-0.13626796057704</v>
@@ -1366,7 +1366,7 @@
         <v>-0.00740902511946132</v>
       </c>
       <c r="I6" t="n">
-        <v>0.181416378387232</v>
+        <v>0.18256157912925</v>
       </c>
       <c r="J6" t="n">
         <v>-0.0114937243976157</v>
@@ -1527,7 +1527,7 @@
         <v>0.0925814739476112</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0621870358794253</v>
+        <v>0.0528375710113693</v>
       </c>
       <c r="J7" t="n">
         <v>-0.18730374035732</v>
@@ -1688,7 +1688,7 @@
         <v>-0.0504494845433958</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.090358557590661</v>
+        <v>-0.086259427946838</v>
       </c>
       <c r="J8" t="n">
         <v>0.312408160364022</v>
@@ -1849,7 +1849,7 @@
         <v>0.0856558050038556</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0508762586951877</v>
+        <v>0.0561817306500833</v>
       </c>
       <c r="J9" t="n">
         <v>-0.207119473504056</v>
@@ -2010,7 +2010,7 @@
         <v>0.0717473776606122</v>
       </c>
       <c r="I10" t="n">
-        <v>0.085485526010238</v>
+        <v>0.0856436659310634</v>
       </c>
       <c r="J10" t="n">
         <v>0.0605231060707927</v>
@@ -2171,7 +2171,7 @@
         <v>0.031015978669683</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0177639160519283</v>
+        <v>0.0115354942825186</v>
       </c>
       <c r="J11" t="n">
         <v>0.308377868489366</v>
@@ -2332,7 +2332,7 @@
         <v>0.0657380702100631</v>
       </c>
       <c r="I12" t="n">
-        <v>0.120078491797855</v>
+        <v>0.126768523858354</v>
       </c>
       <c r="J12" t="n">
         <v>0.466917790334461</v>
@@ -2493,7 +2493,7 @@
         <v>-0.133967244021868</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.237330111423642</v>
+        <v>-0.234525603705115</v>
       </c>
       <c r="J13" t="n">
         <v>-0.166672451259877</v>
